--- a/output/compagnies_not_found.xlsx
+++ b/output/compagnies_not_found.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B245"/>
+  <dimension ref="A1:B212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,12 +623,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hill-rom holdings inc</t>
+          <t>hillrom holdings inc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hill-rom holdings inc</t>
+          <t>hillrom holdings inc</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the mosaic </t>
+          <t xml:space="preserve"> mosaic </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">the mosaic </t>
+          <t xml:space="preserve"> mosaic </t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>mol magyar olaj- es gazipari nyilvanosan mukodo reszvenytarsasag</t>
+          <t>mol magyar olaj es gazipari nyilvanosan mukodo reszvenytarsasag</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mol magyar olaj- es gazipari nyilvanosan mukodo reszvenytarsasag</t>
+          <t>mol magyar olaj es gazipari nyilvanosan mukodo reszvenytarsasag</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>uni-select inc</t>
+          <t>uniselect inc</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>uni-select inc</t>
+          <t>uniselect inc</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>pt bank raya indonesia tbk</t>
+          <t xml:space="preserve"> bank raya indonesia </t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>pt bank raya indonesia tbk</t>
+          <t xml:space="preserve"> bank raya indonesia </t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the scotts miracle-gro </t>
+          <t xml:space="preserve"> scotts miraclegro </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">the scotts miracle-gro </t>
+          <t xml:space="preserve"> scotts miraclegro </t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>public joint-stock  phosagro</t>
+          <t>public jointstock  phosagro</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>public joint-stock  phosagro</t>
+          <t>public jointstock  phosagro</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>ingenico group - gcs</t>
+          <t>ingenico group  gcs</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ingenico group - gcs</t>
+          <t>ingenico group  gcs</t>
         </is>
       </c>
     </row>
@@ -1559,1810 +1559,1414 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">everchina int'l holdings  </t>
+          <t xml:space="preserve">lifestyle communities </t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">everchina int'l holdings  </t>
+          <t xml:space="preserve">lifestyle communities </t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lifestyle communities </t>
+          <t xml:space="preserve">big shopping centers </t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">lifestyle communities </t>
+          <t xml:space="preserve">big shopping centers </t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">big shopping centers </t>
+          <t xml:space="preserve">let group holdings </t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">big shopping centers </t>
+          <t xml:space="preserve">let group holdings </t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">let group holdings </t>
+          <t xml:space="preserve">first sponsor group </t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">let group holdings </t>
+          <t xml:space="preserve">first sponsor group </t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">first sponsor group </t>
+          <t xml:space="preserve">fd technologies </t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">first sponsor group </t>
+          <t xml:space="preserve">fd technologies </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fd technologies </t>
+          <t xml:space="preserve">mp evans group </t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">fd technologies </t>
+          <t xml:space="preserve">mp evans group </t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mp evans group </t>
+          <t xml:space="preserve">edgewell personal care </t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">mp evans group </t>
+          <t xml:space="preserve">edgewell personal care </t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>pt eagle high plantations tbk</t>
+          <t>agromino a/s</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>pt eagle high plantations tbk</t>
+          <t>agromino a/s</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>pt sawit sumbermas sarana tbk</t>
+          <t>brasilagro  companhia brasileira de propriedades agricolas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>pt sawit sumbermas sarana tbk</t>
+          <t>brasilagro  companhia brasileira de propriedades agricolas</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">al-jouf agricultural development </t>
+          <t xml:space="preserve">big camera  public  </t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">al-jouf agricultural development </t>
+          <t xml:space="preserve">big camera  public  </t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>pt inti agri resources tbk</t>
+          <t>bigben interactive</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>pt inti agri resources tbk</t>
+          <t>bigben interactive</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hap seng plantations holdings berhad</t>
+          <t>agt food and ingredients inc</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>hap seng plantations holdings berhad</t>
+          <t>agt food and ingredients inc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>boustead plantations berhad</t>
+          <t xml:space="preserve">chaoda modern agriculture (holdings) </t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>boustead plantations berhad</t>
+          <t xml:space="preserve">chaoda modern agriculture (holdings) </t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>genting plantations berhad</t>
+          <t xml:space="preserve"> perusahaan perkebunan london sumatra indonesia </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>genting plantations berhad</t>
+          <t xml:space="preserve"> perusahaan perkebunan london sumatra indonesia </t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgewell personal care </t>
+          <t>tecon biology coltd</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgewell personal care </t>
+          <t>tecon biology coltd</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>kim loong resources berhad</t>
+          <t xml:space="preserve">hoang anh gia lai agricultural joint stock </t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>kim loong resources berhad</t>
+          <t xml:space="preserve">hoang anh gia lai agricultural joint stock </t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>kluang rubber  (malaya) berhad</t>
+          <t xml:space="preserve">anta sports products </t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>kluang rubber  (malaya) berhad</t>
+          <t xml:space="preserve">anta sports products </t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>agromino a/s</t>
+          <t xml:space="preserve">namchow holdings  </t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>agromino a/s</t>
+          <t xml:space="preserve">namchow holdings  </t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>ioi  berhad</t>
+          <t>public joint stock  inarctica</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ioi  berhad</t>
+          <t>public joint stock  inarctica</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>brasilagro - companhia brasileira de propriedades agricolas</t>
+          <t xml:space="preserve">arabia cotton ginning </t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>brasilagro - companhia brasileira de propriedades agricolas</t>
+          <t xml:space="preserve">arabia cotton ginning </t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bahvest resources berhad</t>
+          <t xml:space="preserve">jazan energy and development </t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>bahvest resources berhad</t>
+          <t xml:space="preserve">jazan energy and development </t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hunan new wellful coltd</t>
+          <t xml:space="preserve">hills </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>hunan new wellful coltd</t>
+          <t xml:space="preserve">hills </t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>pengdu agriculture &amp; animal husbandry coltd</t>
+          <t xml:space="preserve">apc technology group </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>pengdu agriculture &amp; animal husbandry coltd</t>
+          <t xml:space="preserve">apc technology group </t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the a2 milk  </t>
+          <t xml:space="preserve">luxnet </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">the a2 milk  </t>
+          <t xml:space="preserve">luxnet </t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>jiangxi zhengbang technology coltd</t>
+          <t xml:space="preserve">odk solutions  </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>jiangxi zhengbang technology coltd</t>
+          <t xml:space="preserve">odk solutions  </t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">al gassim investment holding </t>
+          <t xml:space="preserve">avigilon </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">al gassim investment holding </t>
+          <t xml:space="preserve">avigilon </t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>shandongdenghai seeds coltd</t>
+          <t>eguardian inc</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>shandongdenghai seeds coltd</t>
+          <t>eguardian inc</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">big camera  public  </t>
+          <t>columbus energy sa</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">big camera  public  </t>
+          <t>columbus energy sa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>pt bakrie sumatera plantations tbk</t>
+          <t xml:space="preserve">keywords studios </t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>pt bakrie sumatera plantations tbk</t>
+          <t xml:space="preserve">keywords studios </t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bigben interactive</t>
+          <t>relief therapeutics holding ag</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>bigben interactive</t>
+          <t>relief therapeutics holding ag</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>far east holdings berhad</t>
+          <t xml:space="preserve">catapult group international </t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>far east holdings berhad</t>
+          <t xml:space="preserve">catapult group international </t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>agt food and ingredients inc</t>
+          <t>csra inc</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>agt food and ingredients inc</t>
+          <t>csra inc</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">chaoda modern agriculture (holdings) </t>
+          <t xml:space="preserve">gentrack group </t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">chaoda modern agriculture (holdings) </t>
+          <t xml:space="preserve">gentrack group </t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>pt perusahaan perkebunan london sumatra indonesia tbk</t>
+          <t xml:space="preserve">nostrum oil &amp; gas </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>pt perusahaan perkebunan london sumatra indonesia tbk</t>
+          <t xml:space="preserve">nostrum oil &amp; gas </t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>public joint stock  "cherkizovo group"</t>
+          <t xml:space="preserve">bonterra energy </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>public joint stock  "cherkizovo group"</t>
+          <t xml:space="preserve">bonterra energy </t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>tecon biology coltd</t>
+          <t>zhejiang hugeleaf coltd</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>tecon biology coltd</t>
+          <t>zhejiang hugeleaf coltd</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hoang anh gia lai agricultural joint stock </t>
+          <t xml:space="preserve">hubei sanonda  </t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">hoang anh gia lai agricultural joint stock </t>
+          <t xml:space="preserve">hubei sanonda  </t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">anta sports products </t>
+          <t>lier chemical coltd</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">anta sports products </t>
+          <t>lier chemical coltd</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">namchow holdings  </t>
+          <t>sichuan lutianhua   by shares</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">namchow holdings  </t>
+          <t>sichuan lutianhua   by shares</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>united malacca berhad</t>
+          <t xml:space="preserve">engro  </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>united malacca berhad</t>
+          <t xml:space="preserve">engro  </t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>public joint stock  inarctica</t>
+          <t xml:space="preserve">sabic agrinutrients </t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>public joint stock  inarctica</t>
+          <t xml:space="preserve">sabic agrinutrients </t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">saudi fisheries </t>
+          <t>nanjing red sun coltd</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">saudi fisheries </t>
+          <t>nanjing red sun coltd</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>tsh resources berhad</t>
+          <t xml:space="preserve"> fertilisers and chemicals travancore </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>tsh resources berhad</t>
+          <t xml:space="preserve"> fertilisers and chemicals travancore </t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">arabia cotton ginning </t>
+          <t>petrovietnam fertilizer and chemicals   jsc</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">arabia cotton ginning </t>
+          <t>petrovietnam fertilizer and chemicals   jsc</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tabuk agricultural development </t>
+          <t>abu qir fertilizers and chemical industries  (sae)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">tabuk agricultural development </t>
+          <t>abu qir fertilizers and chemical industries  (sae)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jazan energy and development </t>
+          <t>apex investment psc</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">jazan energy and development </t>
+          <t>apex investment psc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>sarawak oil palms berhad</t>
+          <t xml:space="preserve">hil </t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>sarawak oil palms berhad</t>
+          <t xml:space="preserve">hil </t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>fgv holdings berhad</t>
+          <t>miquel y costas &amp; miquel sa</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>fgv holdings berhad</t>
+          <t>miquel y costas &amp; miquel sa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hills </t>
+          <t xml:space="preserve">mayer steel pipe </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">hills </t>
+          <t xml:space="preserve">mayer steel pipe </t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">apc technology group </t>
+          <t>qingdao east steel tower stock coltd</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">apc technology group </t>
+          <t>qingdao east steel tower stock coltd</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">luxnet </t>
+          <t>chr hansen holding a/s</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">luxnet </t>
+          <t>chr hansen holding a/s</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">odk solutions  </t>
+          <t>lianhe chemical technology coltd</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">odk solutions  </t>
+          <t>lianhe chemical technology coltd</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">avigilon </t>
+          <t>zhejiang xinan chemical industrial group coltd</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">avigilon </t>
+          <t>zhejiang xinan chemical industrial group coltd</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>e-guardian inc</t>
+          <t>edenred se</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>e-guardian inc</t>
+          <t>edenred se</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>columbus energy sa</t>
+          <t xml:space="preserve">daiseki eco solution  </t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>columbus energy sa</t>
+          <t xml:space="preserve">daiseki eco solution  </t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keywords studios </t>
+          <t>supreme industries inc</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">keywords studios </t>
+          <t>supreme industries inc</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>relief therapeutics holding ag</t>
+          <t>combined group contracting   ksc (public)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>relief therapeutics holding ag</t>
+          <t>combined group contracting   ksc (public)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">catapult group international </t>
+          <t xml:space="preserve">tutor perini </t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">catapult group international </t>
+          <t xml:space="preserve">tutor perini </t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>csra inc</t>
+          <t xml:space="preserve">formation group </t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>csra inc</t>
+          <t xml:space="preserve">formation group </t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gentrack group </t>
+          <t xml:space="preserve">trc construction public  </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">gentrack group </t>
+          <t xml:space="preserve">trc construction public  </t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nostrum oil &amp; gas </t>
+          <t xml:space="preserve">tclarke </t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">nostrum oil &amp; gas </t>
+          <t xml:space="preserve">tclarke </t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonterra energy </t>
+          <t>blue solutions sas</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonterra energy </t>
+          <t>blue solutions sas</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>zhejiang hugeleaf coltd</t>
+          <t>cembre spa</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>zhejiang hugeleaf coltd</t>
+          <t>cembre spa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hubei sanonda  </t>
+          <t xml:space="preserve">meidensha </t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">hubei sanonda  </t>
+          <t xml:space="preserve">meidensha </t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">misr fertilizer production </t>
+          <t xml:space="preserve">sulzer </t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">misr fertilizer production </t>
+          <t xml:space="preserve">sulzer </t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>lier chemical coltd</t>
+          <t>clarcor inc</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>lier chemical coltd</t>
+          <t>clarcor inc</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>w t k holdings berhad</t>
+          <t>daconsortium holdings inc</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>w t k holdings berhad</t>
+          <t>daconsortium holdings inc</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>stanley agriculture group coltd</t>
+          <t xml:space="preserve">caxton and ctp publishers and printers </t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>stanley agriculture group coltd</t>
+          <t xml:space="preserve">caxton and ctp publishers and printers </t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>sichuan lutianhua   by shares</t>
+          <t>chorus aviation inc</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>sichuan lutianhua   by shares</t>
+          <t>chorus aviation inc</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">engro  </t>
+          <t xml:space="preserve">saudi ground services </t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">engro  </t>
+          <t xml:space="preserve">saudi ground services </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sabic agri-nutrients </t>
+          <t xml:space="preserve">precious shipping public  </t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">sabic agri-nutrients </t>
+          <t xml:space="preserve">precious shipping public  </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>nanjing red sun coltd</t>
+          <t>hitachi rail sts spa</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>nanjing red sun coltd</t>
+          <t>hitachi rail sts spa</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the fertilisers and chemicals travancore </t>
+          <t xml:space="preserve">kitano construction </t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">the fertilisers and chemicals travancore </t>
+          <t xml:space="preserve">kitano construction </t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>petrovietnam fertilizer and chemicals  - jsc</t>
+          <t xml:space="preserve">careerlink  </t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>petrovietnam fertilizer and chemicals  - jsc</t>
+          <t xml:space="preserve">careerlink  </t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>abu qir fertilizers and chemical industries  (sae)</t>
+          <t>hill international inc</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>abu qir fertilizers and chemical industries  (sae)</t>
+          <t>hill international inc</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>apex investment psc</t>
+          <t xml:space="preserve"> bw plantation </t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>apex investment psc</t>
+          <t xml:space="preserve"> bw plantation </t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hil </t>
+          <t>masmovil ibercom sa</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">hil </t>
+          <t>masmovil ibercom sa</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>miquel y costas &amp; miquel sa</t>
+          <t xml:space="preserve">beijing jingneng clean energy  </t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>miquel y costas &amp; miquel sa</t>
+          <t xml:space="preserve">beijing jingneng clean energy  </t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mayer steel pipe </t>
+          <t xml:space="preserve">ausnet pty </t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">mayer steel pipe </t>
+          <t xml:space="preserve">ausnet pty </t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>qingdao east steel tower stock coltd</t>
+          <t>erex coltd</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>qingdao east steel tower stock coltd</t>
+          <t>erex coltd</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>jaya tiasa holdings berhad</t>
+          <t>cameleon software sa</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jaya tiasa holdings berhad</t>
+          <t>cameleon software sa</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>chr hansen holding a/s</t>
+          <t>stallergenes sa</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>chr hansen holding a/s</t>
+          <t>stallergenes sa</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>lianhe chemical technology coltd</t>
+          <t>recif technologies sas</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>lianhe chemical technology coltd</t>
+          <t>recif technologies sas</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>zhejiang xinan chemical industrial group coltd</t>
+          <t>pcf group spolka akcyjna</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>zhejiang xinan chemical industrial group coltd</t>
+          <t>pcf group spolka akcyjna</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>edenred se</t>
+          <t>grupa interiapl sp z oo spk</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>edenred se</t>
+          <t>grupa interiapl sp z oo spk</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">daiseki eco solution  </t>
+          <t xml:space="preserve"> mora telematika indonesia</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">daiseki eco solution  </t>
+          <t xml:space="preserve"> mora telematika indonesia</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>supreme industries inc</t>
+          <t>precision biosciences inc</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>supreme industries inc</t>
+          <t>precision biosciences inc</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>combined group contracting  - ksc (public)</t>
+          <t xml:space="preserve">zhongan online p &amp; c insurance  </t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>combined group contracting  - ksc (public)</t>
+          <t xml:space="preserve">zhongan online p &amp; c insurance  </t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tutor perini </t>
+          <t>bhg group ab (publ)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">tutor perini </t>
+          <t>bhg group ab (publ)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">formation group </t>
+          <t>agilon health inc</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">formation group </t>
+          <t>agilon health inc</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">trc construction public  </t>
+          <t xml:space="preserve">oro  </t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">trc construction public  </t>
+          <t xml:space="preserve">oro  </t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tclarke </t>
+          <t>spire global inc</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">tclarke </t>
+          <t>spire global inc</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>blue solutions sas</t>
+          <t>advent technologies holdings inc</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>blue solutions sas</t>
+          <t>advent technologies holdings inc</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>cembre spa</t>
+          <t xml:space="preserve">masco </t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>cembre spa</t>
+          <t xml:space="preserve">masco </t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">meidensha </t>
+          <t>sas florentaise</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">meidensha </t>
+          <t>sas florentaise</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sulzer </t>
+          <t>navigator paper figueira sa</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">sulzer </t>
+          <t>navigator paper figueira sa</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>clarcor inc</t>
+          <t>granitifiandre spa</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>clarcor inc</t>
+          <t>granitifiandre spa</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>daconsortium holdings inc</t>
+          <t>steuler fliesengruppe ag</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>daconsortium holdings inc</t>
+          <t>steuler fliesengruppe ag</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">caxton and ctp publishers and printers </t>
+          <t>public joint stock  nakhodka active marine fishery base</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">caxton and ctp publishers and printers </t>
+          <t>public joint stock  nakhodka active marine fishery base</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>chorus aviation inc</t>
+          <t>hailir pesticides and chemicals group coltd</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>chorus aviation inc</t>
+          <t>hailir pesticides and chemicals group coltd</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">saudi ground services </t>
+          <t>jiangsu provincial agricultural reclamation and development coltd</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">saudi ground services </t>
+          <t>jiangsu provincial agricultural reclamation and development coltd</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">precious shipping public  </t>
+          <t>mlinostroj dd</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">precious shipping public  </t>
+          <t>mlinostroj dd</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>hitachi rail sts spa</t>
+          <t>sc morarit panificatie roman sa</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>hitachi rail sts spa</t>
+          <t>sc morarit panificatie roman sa</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitano construction </t>
+          <t>ahorro familiar sa</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitano construction </t>
+          <t>ahorro familiar sa</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">careerlink  </t>
+          <t xml:space="preserve">reflec </t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">careerlink  </t>
+          <t xml:space="preserve">reflec </t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>hill international inc</t>
+          <t>c bechstein pianofortefabrik ag</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>hill international inc</t>
+          <t>c bechstein pianofortefabrik ag</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>pt bw plantation tbk</t>
+          <t xml:space="preserve">evoqua water technologies </t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>pt bw plantation tbk</t>
+          <t xml:space="preserve">evoqua water technologies </t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>masmovil ibercom sa</t>
+          <t>sphera franchise group sa</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>masmovil ibercom sa</t>
+          <t>sphera franchise group sa</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">beijing jingneng clean energy  </t>
+          <t xml:space="preserve">argo blockchain </t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">beijing jingneng clean energy  </t>
+          <t xml:space="preserve">argo blockchain </t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ausnet pty </t>
+          <t>ast spacemobile inc</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">ausnet pty </t>
+          <t>ast spacemobile inc</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>erex coltd</t>
+          <t>murales</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>erex coltd</t>
+          <t>murales</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>cameleon software sa</t>
+          <t>tekstil proizvodno in trgovsko podjetje dd</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>cameleon software sa</t>
+          <t>tekstil proizvodno in trgovsko podjetje dd</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>stallergenes sa</t>
+          <t>encavis ag</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>stallergenes sa</t>
+          <t>encavis ag</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>recif technologies sas</t>
+          <t xml:space="preserve">big technologies </t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>recif technologies sas</t>
+          <t xml:space="preserve">big technologies </t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>pcf group spolka akcyjna</t>
+          <t>aa tech srl</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>pcf group spolka akcyjna</t>
+          <t>aa tech srl</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>grupa interiapl sp z oo spk</t>
+          <t>apontis pharma ag</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>grupa interiapl sp z oo spk</t>
+          <t>apontis pharma ag</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>pt mora telematika indonesia</t>
+          <t>byggfakta group nordic holdco ab (publ)</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>pt mora telematika indonesia</t>
+          <t>byggfakta group nordic holdco ab (publ)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>precision biosciences inc</t>
+          <t>arctic stream sa</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
-        <is>
-          <t>precision biosciences inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zhongan online p &amp; c insurance  </t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zhongan online p &amp; c insurance  </t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="1" t="inlineStr">
-        <is>
-          <t>bhg group ab (publ)</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>bhg group ab (publ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="1" t="inlineStr">
-        <is>
-          <t>agilon health inc</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>agilon health inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oro  </t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oro  </t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="1" t="inlineStr">
-        <is>
-          <t>spire global inc</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>spire global inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="1" t="inlineStr">
-        <is>
-          <t>advent technologies holdings inc</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>advent technologies holdings inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">masco </t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">masco </t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="1" t="inlineStr">
-        <is>
-          <t>sas florentaise</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>sas florentaise</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="1" t="inlineStr">
-        <is>
-          <t>navigator paper figueira sa</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>navigator paper figueira sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="1" t="inlineStr">
-        <is>
-          <t>granitifiandre spa</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>granitifiandre spa</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="1" t="inlineStr">
-        <is>
-          <t>steuler fliesengruppe ag</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>steuler fliesengruppe ag</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="1" t="inlineStr">
-        <is>
-          <t>public joint stock  nakhodka active marine fishery base</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>public joint stock  nakhodka active marine fishery base</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="1" t="inlineStr">
-        <is>
-          <t>hailir pesticides and chemicals group coltd</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>hailir pesticides and chemicals group coltd</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="1" t="inlineStr">
-        <is>
-          <t>jiangsu provincial agricultural reclamation and development coltd</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>jiangsu provincial agricultural reclamation and development coltd</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="1" t="inlineStr">
-        <is>
-          <t>mlinostroj dd</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>mlinostroj dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="1" t="inlineStr">
-        <is>
-          <t>sc morarit panificatie roman sa</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>sc morarit panificatie roman sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="1" t="inlineStr">
-        <is>
-          <t>ahorro familiar sa</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>ahorro familiar sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reflec </t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reflec </t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="1" t="inlineStr">
-        <is>
-          <t>c bechstein pianofortefabrik ag</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>c bechstein pianofortefabrik ag</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="1" t="inlineStr">
-        <is>
-          <t>leong hup international berhad</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>leong hup international berhad</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">evoqua water technologies </t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">evoqua water technologies </t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="1" t="inlineStr">
-        <is>
-          <t>sphera franchise group sa</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>sphera franchise group sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="1" t="inlineStr">
-        <is>
-          <t>hextar global berhad</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>hextar global berhad</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">argo blockchain </t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">argo blockchain </t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="1" t="inlineStr">
-        <is>
-          <t>ast spacemobile inc</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>ast spacemobile inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="1" t="inlineStr">
-        <is>
-          <t>murales</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>murales</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="1" t="inlineStr">
-        <is>
-          <t>tekstil proizvodno in trgovsko podjetje dd</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>tekstil proizvodno in trgovsko podjetje dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="1" t="inlineStr">
-        <is>
-          <t>encavis ag</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>encavis ag</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">big technologies </t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">big technologies </t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="1" t="inlineStr">
-        <is>
-          <t>aa tech srl</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>aa tech srl</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="1" t="inlineStr">
-        <is>
-          <t>apontis pharma ag</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>apontis pharma ag</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="1" t="inlineStr">
-        <is>
-          <t>byggfakta group nordic holdco ab (publ)</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>byggfakta group nordic holdco ab (publ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="1" t="inlineStr">
-        <is>
-          <t>arctic stream sa</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
         <is>
           <t>arctic stream sa</t>
         </is>

--- a/output/compagnies_not_found.xlsx
+++ b/output/compagnies_not_found.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B212"/>
+  <dimension ref="A1:B214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1787,1186 +1787,1210 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">arabia cotton ginning </t>
+          <t>vilmorin &amp; cie sa</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">arabia cotton ginning </t>
+          <t>vilmorin &amp; cie sa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jazan energy and development </t>
+          <t xml:space="preserve">arabia cotton ginning </t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">jazan energy and development </t>
+          <t xml:space="preserve">arabia cotton ginning </t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hills </t>
+          <t xml:space="preserve">jazan energy and development </t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">hills </t>
+          <t xml:space="preserve">jazan energy and development </t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">apc technology group </t>
+          <t xml:space="preserve">hills </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">apc technology group </t>
+          <t xml:space="preserve">hills </t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">luxnet </t>
+          <t xml:space="preserve">apc technology group </t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">luxnet </t>
+          <t xml:space="preserve">apc technology group </t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">odk solutions  </t>
+          <t xml:space="preserve">luxnet </t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">odk solutions  </t>
+          <t xml:space="preserve">luxnet </t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">avigilon </t>
+          <t xml:space="preserve">odk solutions  </t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">avigilon </t>
+          <t xml:space="preserve">odk solutions  </t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>eguardian inc</t>
+          <t xml:space="preserve">avigilon </t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>eguardian inc</t>
+          <t xml:space="preserve">avigilon </t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>columbus energy sa</t>
+          <t>eguardian inc</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>columbus energy sa</t>
+          <t>eguardian inc</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keywords studios </t>
+          <t>columbus energy sa</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">keywords studios </t>
+          <t>columbus energy sa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>relief therapeutics holding ag</t>
+          <t xml:space="preserve">keywords studios </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>relief therapeutics holding ag</t>
+          <t xml:space="preserve">keywords studios </t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">catapult group international </t>
+          <t>relief therapeutics holding ag</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">catapult group international </t>
+          <t>relief therapeutics holding ag</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>csra inc</t>
+          <t xml:space="preserve">catapult group international </t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>csra inc</t>
+          <t xml:space="preserve">catapult group international </t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gentrack group </t>
+          <t>csra inc</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">gentrack group </t>
+          <t>csra inc</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nostrum oil &amp; gas </t>
+          <t xml:space="preserve">gentrack group </t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">nostrum oil &amp; gas </t>
+          <t xml:space="preserve">gentrack group </t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonterra energy </t>
+          <t xml:space="preserve">nostrum oil &amp; gas </t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">bonterra energy </t>
+          <t xml:space="preserve">nostrum oil &amp; gas </t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>zhejiang hugeleaf coltd</t>
+          <t xml:space="preserve">bonterra energy </t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>zhejiang hugeleaf coltd</t>
+          <t xml:space="preserve">bonterra energy </t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hubei sanonda  </t>
+          <t>zhejiang hugeleaf coltd</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">hubei sanonda  </t>
+          <t>zhejiang hugeleaf coltd</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>lier chemical coltd</t>
+          <t xml:space="preserve">hubei sanonda  </t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>lier chemical coltd</t>
+          <t xml:space="preserve">hubei sanonda  </t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>sichuan lutianhua   by shares</t>
+          <t>lier chemical coltd</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>sichuan lutianhua   by shares</t>
+          <t>lier chemical coltd</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">engro  </t>
+          <t xml:space="preserve">stanley agricultural group  </t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">engro  </t>
+          <t xml:space="preserve">stanley agricultural group  </t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sabic agrinutrients </t>
+          <t>sichuan lutianhua   by shares</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">sabic agrinutrients </t>
+          <t>sichuan lutianhua   by shares</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>nanjing red sun coltd</t>
+          <t xml:space="preserve">engro  </t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nanjing red sun coltd</t>
+          <t xml:space="preserve">engro  </t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> fertilisers and chemicals travancore </t>
+          <t xml:space="preserve">sabic agrinutrients </t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> fertilisers and chemicals travancore </t>
+          <t xml:space="preserve">sabic agrinutrients </t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>petrovietnam fertilizer and chemicals   jsc</t>
+          <t>nanjing red sun coltd</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>petrovietnam fertilizer and chemicals   jsc</t>
+          <t>nanjing red sun coltd</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>abu qir fertilizers and chemical industries  (sae)</t>
+          <t xml:space="preserve"> fertilisers and chemicals travancore </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>abu qir fertilizers and chemical industries  (sae)</t>
+          <t xml:space="preserve"> fertilisers and chemicals travancore </t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>apex investment psc</t>
+          <t>petrovietnam fertilizer and chemicals   jsc</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>apex investment psc</t>
+          <t>petrovietnam fertilizer and chemicals   jsc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hil </t>
+          <t>abu qir fertilizers and chemical industries  (sae)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">hil </t>
+          <t>abu qir fertilizers and chemical industries  (sae)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>miquel y costas &amp; miquel sa</t>
+          <t>apex investment psc</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>miquel y costas &amp; miquel sa</t>
+          <t>apex investment psc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mayer steel pipe </t>
+          <t xml:space="preserve">hil </t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">mayer steel pipe </t>
+          <t xml:space="preserve">hil </t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>qingdao east steel tower stock coltd</t>
+          <t>miquel y costas &amp; miquel sa</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>qingdao east steel tower stock coltd</t>
+          <t>miquel y costas &amp; miquel sa</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>chr hansen holding a/s</t>
+          <t xml:space="preserve">mayer steel pipe </t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>chr hansen holding a/s</t>
+          <t xml:space="preserve">mayer steel pipe </t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>lianhe chemical technology coltd</t>
+          <t>qingdao east steel tower stock coltd</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>lianhe chemical technology coltd</t>
+          <t>qingdao east steel tower stock coltd</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>zhejiang xinan chemical industrial group coltd</t>
+          <t>chr hansen holding a/s</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>zhejiang xinan chemical industrial group coltd</t>
+          <t>chr hansen holding a/s</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>edenred se</t>
+          <t>lianhe chemical technology coltd</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>edenred se</t>
+          <t>lianhe chemical technology coltd</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">daiseki eco solution  </t>
+          <t>zhejiang xinan chemical industrial group coltd</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">daiseki eco solution  </t>
+          <t>zhejiang xinan chemical industrial group coltd</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>supreme industries inc</t>
+          <t>edenred se</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>supreme industries inc</t>
+          <t>edenred se</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>combined group contracting   ksc (public)</t>
+          <t xml:space="preserve">daiseki eco solution  </t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>combined group contracting   ksc (public)</t>
+          <t xml:space="preserve">daiseki eco solution  </t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tutor perini </t>
+          <t>supreme industries inc</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">tutor perini </t>
+          <t>supreme industries inc</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">formation group </t>
+          <t>combined group contracting   ksc (public)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">formation group </t>
+          <t>combined group contracting   ksc (public)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">trc construction public  </t>
+          <t xml:space="preserve">tutor perini </t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">trc construction public  </t>
+          <t xml:space="preserve">tutor perini </t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tclarke </t>
+          <t xml:space="preserve">formation group </t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">tclarke </t>
+          <t xml:space="preserve">formation group </t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>blue solutions sas</t>
+          <t xml:space="preserve">trc construction public  </t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>blue solutions sas</t>
+          <t xml:space="preserve">trc construction public  </t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>cembre spa</t>
+          <t xml:space="preserve">tclarke </t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>cembre spa</t>
+          <t xml:space="preserve">tclarke </t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">meidensha </t>
+          <t>blue solutions sas</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">meidensha </t>
+          <t>blue solutions sas</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sulzer </t>
+          <t>cembre spa</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">sulzer </t>
+          <t>cembre spa</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>clarcor inc</t>
+          <t xml:space="preserve">meidensha </t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>clarcor inc</t>
+          <t xml:space="preserve">meidensha </t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>daconsortium holdings inc</t>
+          <t xml:space="preserve">sulzer </t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>daconsortium holdings inc</t>
+          <t xml:space="preserve">sulzer </t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">caxton and ctp publishers and printers </t>
+          <t>clarcor inc</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">caxton and ctp publishers and printers </t>
+          <t>clarcor inc</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>chorus aviation inc</t>
+          <t>daconsortium holdings inc</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>chorus aviation inc</t>
+          <t>daconsortium holdings inc</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">saudi ground services </t>
+          <t xml:space="preserve">caxton and ctp publishers and printers </t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">saudi ground services </t>
+          <t xml:space="preserve">caxton and ctp publishers and printers </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">precious shipping public  </t>
+          <t>chorus aviation inc</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">precious shipping public  </t>
+          <t>chorus aviation inc</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>hitachi rail sts spa</t>
+          <t xml:space="preserve">saudi ground services </t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>hitachi rail sts spa</t>
+          <t xml:space="preserve">saudi ground services </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitano construction </t>
+          <t xml:space="preserve">precious shipping public  </t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitano construction </t>
+          <t xml:space="preserve">precious shipping public  </t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">careerlink  </t>
+          <t>hitachi rail sts spa</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">careerlink  </t>
+          <t>hitachi rail sts spa</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>hill international inc</t>
+          <t xml:space="preserve">kitano construction </t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>hill international inc</t>
+          <t xml:space="preserve">kitano construction </t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> bw plantation </t>
+          <t xml:space="preserve">careerlink  </t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> bw plantation </t>
+          <t xml:space="preserve">careerlink  </t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>masmovil ibercom sa</t>
+          <t>hill international inc</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>masmovil ibercom sa</t>
+          <t>hill international inc</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">beijing jingneng clean energy  </t>
+          <t xml:space="preserve"> bw plantation </t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">beijing jingneng clean energy  </t>
+          <t xml:space="preserve"> bw plantation </t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ausnet pty </t>
+          <t>masmovil ibercom sa</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">ausnet pty </t>
+          <t>masmovil ibercom sa</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>erex coltd</t>
+          <t xml:space="preserve">beijing jingneng clean energy  </t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>erex coltd</t>
+          <t xml:space="preserve">beijing jingneng clean energy  </t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>cameleon software sa</t>
+          <t xml:space="preserve">ausnet pty </t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>cameleon software sa</t>
+          <t xml:space="preserve">ausnet pty </t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>stallergenes sa</t>
+          <t>erex coltd</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>stallergenes sa</t>
+          <t>erex coltd</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>recif technologies sas</t>
+          <t>cameleon software sa</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>recif technologies sas</t>
+          <t>cameleon software sa</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>pcf group spolka akcyjna</t>
+          <t>stallergenes sa</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>pcf group spolka akcyjna</t>
+          <t>stallergenes sa</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>grupa interiapl sp z oo spk</t>
+          <t>recif technologies sas</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>grupa interiapl sp z oo spk</t>
+          <t>recif technologies sas</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> mora telematika indonesia</t>
+          <t>pcf group spolka akcyjna</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> mora telematika indonesia</t>
+          <t>pcf group spolka akcyjna</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>precision biosciences inc</t>
+          <t>grupa interiapl sp z oo spk</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>precision biosciences inc</t>
+          <t>grupa interiapl sp z oo spk</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">zhongan online p &amp; c insurance  </t>
+          <t xml:space="preserve"> mora telematika indonesia</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">zhongan online p &amp; c insurance  </t>
+          <t xml:space="preserve"> mora telematika indonesia</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>bhg group ab (publ)</t>
+          <t>precision biosciences inc</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>bhg group ab (publ)</t>
+          <t>precision biosciences inc</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>agilon health inc</t>
+          <t xml:space="preserve">zhongan online p &amp; c insurance  </t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>agilon health inc</t>
+          <t xml:space="preserve">zhongan online p &amp; c insurance  </t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">oro  </t>
+          <t>bhg group ab (publ)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">oro  </t>
+          <t>bhg group ab (publ)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>spire global inc</t>
+          <t>agilon health inc</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>spire global inc</t>
+          <t>agilon health inc</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>advent technologies holdings inc</t>
+          <t xml:space="preserve">oro  </t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>advent technologies holdings inc</t>
+          <t xml:space="preserve">oro  </t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">masco </t>
+          <t>spire global inc</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">masco </t>
+          <t>spire global inc</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>sas florentaise</t>
+          <t>advent technologies holdings inc</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>sas florentaise</t>
+          <t>advent technologies holdings inc</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>navigator paper figueira sa</t>
+          <t xml:space="preserve">masco </t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>navigator paper figueira sa</t>
+          <t xml:space="preserve">masco </t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>granitifiandre spa</t>
+          <t>sas florentaise</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>granitifiandre spa</t>
+          <t>sas florentaise</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>steuler fliesengruppe ag</t>
+          <t>navigator paper figueira sa</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>steuler fliesengruppe ag</t>
+          <t>navigator paper figueira sa</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>public joint stock  nakhodka active marine fishery base</t>
+          <t>granitifiandre spa</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>public joint stock  nakhodka active marine fishery base</t>
+          <t>granitifiandre spa</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>hailir pesticides and chemicals group coltd</t>
+          <t>steuler fliesengruppe ag</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>hailir pesticides and chemicals group coltd</t>
+          <t>steuler fliesengruppe ag</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>jiangsu provincial agricultural reclamation and development coltd</t>
+          <t>public joint stock  nakhodka active marine fishery base</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>jiangsu provincial agricultural reclamation and development coltd</t>
+          <t>public joint stock  nakhodka active marine fishery base</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>mlinostroj dd</t>
+          <t>hailir pesticides and chemicals group coltd</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>mlinostroj dd</t>
+          <t>hailir pesticides and chemicals group coltd</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>sc morarit panificatie roman sa</t>
+          <t>jiangsu provincial agricultural reclamation and development coltd</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>sc morarit panificatie roman sa</t>
+          <t>jiangsu provincial agricultural reclamation and development coltd</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>ahorro familiar sa</t>
+          <t>mlinostroj dd</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ahorro familiar sa</t>
+          <t>mlinostroj dd</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">reflec </t>
+          <t>sc morarit panificatie roman sa</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">reflec </t>
+          <t>sc morarit panificatie roman sa</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>c bechstein pianofortefabrik ag</t>
+          <t>ahorro familiar sa</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>c bechstein pianofortefabrik ag</t>
+          <t>ahorro familiar sa</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">evoqua water technologies </t>
+          <t xml:space="preserve">reflec </t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">evoqua water technologies </t>
+          <t xml:space="preserve">reflec </t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>sphera franchise group sa</t>
+          <t>c bechstein pianofortefabrik ag</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>sphera franchise group sa</t>
+          <t>c bechstein pianofortefabrik ag</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">argo blockchain </t>
+          <t xml:space="preserve">evoqua water technologies </t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">argo blockchain </t>
+          <t xml:space="preserve">evoqua water technologies </t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>ast spacemobile inc</t>
+          <t>sphera franchise group sa</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ast spacemobile inc</t>
+          <t>sphera franchise group sa</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>murales</t>
+          <t xml:space="preserve">argo blockchain </t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>murales</t>
+          <t xml:space="preserve">argo blockchain </t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>tekstil proizvodno in trgovsko podjetje dd</t>
+          <t>ast spacemobile inc</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>tekstil proizvodno in trgovsko podjetje dd</t>
+          <t>ast spacemobile inc</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>encavis ag</t>
+          <t>murales</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>encavis ag</t>
+          <t>murales</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">big technologies </t>
+          <t>tekstil proizvodno in trgovsko podjetje dd</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">big technologies </t>
+          <t>tekstil proizvodno in trgovsko podjetje dd</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>aa tech srl</t>
+          <t>encavis ag</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>aa tech srl</t>
+          <t>encavis ag</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>apontis pharma ag</t>
+          <t xml:space="preserve">big technologies </t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>apontis pharma ag</t>
+          <t xml:space="preserve">big technologies </t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>byggfakta group nordic holdco ab (publ)</t>
+          <t>aa tech srl</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>byggfakta group nordic holdco ab (publ)</t>
+          <t>aa tech srl</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
+          <t>apontis pharma ag</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>apontis pharma ag</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>byggfakta group nordic holdco ab (publ)</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>byggfakta group nordic holdco ab (publ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
           <t>arctic stream sa</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>arctic stream sa</t>
         </is>
